--- a/data/trans_bre/P6903-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6903-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 23,74</t>
+          <t>-13,85; 21,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 25,29</t>
+          <t>-13,2; 25,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 19,52</t>
+          <t>-35,65; 14,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 43,73</t>
+          <t>-15,33; 44,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 87,87</t>
+          <t>-35,61; 71,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,12; 162,18</t>
+          <t>-43,0; 150,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 45,17</t>
+          <t>-60,7; 32,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 182,44</t>
+          <t>-33,15; 148,83</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 12,59</t>
+          <t>-8,72; 12,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 23,99</t>
+          <t>1,84; 23,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 16,04</t>
+          <t>-6,3; 15,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 13,1</t>
+          <t>-12,19; 13,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 45,24</t>
+          <t>-25,77; 45,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 113,19</t>
+          <t>5,88; 117,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 48,95</t>
+          <t>-15,27; 44,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 44,91</t>
+          <t>-32,94; 46,88</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 9,2</t>
+          <t>-19,6; 9,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 26,43</t>
+          <t>-9,16; 28,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 27,73</t>
+          <t>-9,52; 25,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 25,06</t>
+          <t>-7,47; 24,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,18; 46,84</t>
+          <t>-55,2; 45,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,85; 209,39</t>
+          <t>-34,69; 231,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 140,6</t>
+          <t>-23,94; 121,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 99,6</t>
+          <t>-16,72; 103,64</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 8,23</t>
+          <t>-8,31; 6,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 19,02</t>
+          <t>2,5; 18,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 11,6</t>
+          <t>-6,25; 10,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 12,75</t>
+          <t>-6,99; 13,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 30,33</t>
+          <t>-24,54; 22,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 90,02</t>
+          <t>9,7; 87,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 32,64</t>
+          <t>-14,98; 28,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 41,53</t>
+          <t>-18,15; 43,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6903-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6903-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>-2,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>-6,6%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 21,1</t>
+          <t>-13,94; 21,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 25,7</t>
+          <t>-13,41; 24,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 14,44</t>
+          <t>-33,13; 18,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 44,73</t>
+          <t>-26,29; 20,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,61; 71,96</t>
+          <t>-37,56; 72,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,0; 150,01</t>
+          <t>-43,14; 171,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,7; 32,19</t>
+          <t>-56,98; 43,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 148,83</t>
+          <t>-48,42; 69,1</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>7,5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 12,86</t>
+          <t>-9,29; 11,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 23,82</t>
+          <t>1,97; 24,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 15,09</t>
+          <t>-6,31; 15,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 13,35</t>
+          <t>-1,02; 16,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 45,92</t>
+          <t>-28,29; 41,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 117,4</t>
+          <t>6,48; 117,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 44,9</t>
+          <t>-14,65; 47,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,94; 46,88</t>
+          <t>-3,6; 55,81</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,7</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 9,6</t>
+          <t>-21,49; 9,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 28,24</t>
+          <t>-9,06; 27,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 25,53</t>
+          <t>-7,31; 25,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 24,97</t>
+          <t>-11,6; 21,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,2; 45,61</t>
+          <t>-59,16; 40,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 231,77</t>
+          <t>-39,58; 242,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 121,14</t>
+          <t>-20,99; 113,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 103,64</t>
+          <t>-23,35; 75,92</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>6,58</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 6,57</t>
+          <t>-8,59; 6,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 18,2</t>
+          <t>2,19; 18,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 10,24</t>
+          <t>-5,71; 11,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 13,55</t>
+          <t>-0,73; 13,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 22,58</t>
+          <t>-25,27; 23,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 87,61</t>
+          <t>8,15; 90,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 28,93</t>
+          <t>-13,61; 33,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 43,46</t>
+          <t>-1,95; 43,52</t>
         </is>
       </c>
     </row>
